--- a/4.evidence/ITGC/UserRegistration_SampleTransactionList_FY2025.xlsx
+++ b/4.evidence/ITGC/UserRegistration_SampleTransactionList_FY2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="サンプルリスト" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="サンプルリスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -143,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -161,7 +160,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -554,6 +556,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -612,12 +615,13 @@
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>ITGC-AC-001_25件対応_RAW_*.csv / 代表5件の申請書PDF</t>
+          <t>SAP_SU01_UserMaster_ChangeHistory_FY2025.csv / 代表5件の申請書PDF</t>
         </is>
       </c>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="5" t="n"/>
     </row>
+    <row r="8"/>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
@@ -660,7 +664,7 @@
           <t>USER-REG-2025-0001</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="10" t="n">
         <v>45903</v>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -688,7 +692,7 @@
           <t>USER-REG-2025-0002</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="10" t="n">
         <v>46036</v>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -716,7 +720,7 @@
           <t>USER-REG-2025-0003</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="10" t="n">
         <v>46000</v>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -744,7 +748,7 @@
           <t>USER-REG-2025-0004</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="10" t="n">
         <v>45870</v>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -772,7 +776,7 @@
           <t>USER-REG-2025-0005</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="10" t="n">
         <v>45816</v>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -800,7 +804,7 @@
           <t>USER-REG-2025-0006</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="10" t="n">
         <v>45882</v>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -828,7 +832,7 @@
           <t>USER-REG-2025-0007</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="10" t="n">
         <v>45916</v>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -856,7 +860,7 @@
           <t>USER-REG-2025-0008</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="10" t="n">
         <v>45763</v>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -884,7 +888,7 @@
           <t>USER-REG-2025-0009</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="10" t="n">
         <v>46070</v>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -912,7 +916,7 @@
           <t>USER-REG-2025-0010</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="10" t="n">
         <v>45797</v>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -940,7 +944,7 @@
           <t>USER-REG-2025-0011</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="10" t="n">
         <v>45751</v>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -955,7 +959,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>MM_USER,PO_CREATE</t>
+          <t>MM_USER</t>
         </is>
       </c>
     </row>
@@ -968,7 +972,7 @@
           <t>USER-REG-2025-0012</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="10" t="n">
         <v>45903</v>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -996,7 +1000,7 @@
           <t>USER-REG-2025-0013</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="10" t="n">
         <v>45909</v>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -1024,7 +1028,7 @@
           <t>USER-REG-2025-0014</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="10" t="n">
         <v>45997</v>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -1052,7 +1056,7 @@
           <t>USER-REG-2025-0015</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="10" t="n">
         <v>46064</v>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1080,7 +1084,7 @@
           <t>USER-REG-2025-0016</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="10" t="n">
         <v>45965</v>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -1108,7 +1112,7 @@
           <t>USER-REG-2025-0017</t>
         </is>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C26" s="10" t="n">
         <v>45986</v>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -1136,7 +1140,7 @@
           <t>USER-REG-2025-0018</t>
         </is>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="10" t="n">
         <v>45963</v>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -1164,7 +1168,7 @@
           <t>USER-REG-2025-0019</t>
         </is>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C28" s="10" t="n">
         <v>45949</v>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -1192,7 +1196,7 @@
           <t>USER-REG-2025-0020</t>
         </is>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" s="10" t="n">
         <v>46029</v>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -1220,7 +1224,7 @@
           <t>USER-REG-2025-0021</t>
         </is>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="C30" s="10" t="n">
         <v>45858</v>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -1248,7 +1252,7 @@
           <t>USER-REG-2025-0022</t>
         </is>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="10" t="n">
         <v>46094</v>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -1263,7 +1267,7 @@
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>SD_USER</t>
+          <t>QM_USER</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1280,7 @@
           <t>USER-REG-2025-0023</t>
         </is>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="C32" s="10" t="n">
         <v>45788</v>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -1304,7 +1308,7 @@
           <t>USER-REG-2025-0024</t>
         </is>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C33" s="10" t="n">
         <v>45904</v>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -1332,7 +1336,7 @@
           <t>USER-REG-2025-0025</t>
         </is>
       </c>
-      <c r="C34" s="9" t="n">
+      <c r="C34" s="10" t="n">
         <v>45873</v>
       </c>
       <c r="D34" s="8" t="inlineStr">
